--- a/backend/uploads/BSEM1201F.xlsx
+++ b/backend/uploads/BSEM1201F.xlsx
@@ -1,240 +1,235 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abbf0957561ee885/Desktop/GUI for the rfid system/RFID_Attendance_System-SDG4/backend/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC1048C9F99957EE5BDE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832D3DB9-489E-4889-8F3C-3D0D15B59180}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6C0973B0D350DB152501C0F0505ED87656CD0302" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7ED8B41-7E67-46A8-A6F5-4B59A7B735DB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
+    <t>RFID_UID</t>
+  </si>
+  <si>
+    <t>Student_ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Week1_Arrival</t>
+  </si>
+  <si>
+    <t>Week1_Departure</t>
+  </si>
+  <si>
+    <t>Week1_Status</t>
+  </si>
+  <si>
+    <t>Week2_Arrival</t>
+  </si>
+  <si>
+    <t>Week2_Departure</t>
+  </si>
+  <si>
+    <t>Week2_Status</t>
+  </si>
+  <si>
+    <t>Week3_Arrival</t>
+  </si>
+  <si>
+    <t>Week3_Departure</t>
+  </si>
+  <si>
+    <t>Week3_Status</t>
+  </si>
+  <si>
+    <t>Week4_Arrival</t>
+  </si>
+  <si>
+    <t>Week4_Departure</t>
+  </si>
+  <si>
+    <t>Week4_Status</t>
+  </si>
+  <si>
+    <t>Week5_Arrival</t>
+  </si>
+  <si>
+    <t>Week5_Departure</t>
+  </si>
+  <si>
+    <t>Week5_Status</t>
+  </si>
+  <si>
+    <t>Week6_Arrival</t>
+  </si>
+  <si>
+    <t>Week6_Departure</t>
+  </si>
+  <si>
+    <t>Week6_Status</t>
+  </si>
+  <si>
+    <t>Week7_Arrival</t>
+  </si>
+  <si>
+    <t>Week7_Departure</t>
+  </si>
+  <si>
+    <t>Week7_Status</t>
+  </si>
+  <si>
+    <t>Week8_Arrival</t>
+  </si>
+  <si>
+    <t>Week8_Departure</t>
+  </si>
+  <si>
+    <t>Week8_Status</t>
+  </si>
+  <si>
+    <t>Week9_Arrival</t>
+  </si>
+  <si>
+    <t>Week9_Departure</t>
+  </si>
+  <si>
+    <t>Week9_Status</t>
+  </si>
+  <si>
+    <t>Week10_Arrival</t>
+  </si>
+  <si>
+    <t>Week10_Departure</t>
+  </si>
+  <si>
+    <t>Week10_Status</t>
+  </si>
+  <si>
+    <t>Week11_Arrival</t>
+  </si>
+  <si>
+    <t>Week11_Departure</t>
+  </si>
+  <si>
+    <t>Week11_Status</t>
+  </si>
+  <si>
+    <t>Week12_Arrival</t>
+  </si>
+  <si>
+    <t>Week12_Departure</t>
+  </si>
+  <si>
+    <t>Week12_Status</t>
+  </si>
+  <si>
+    <t>Total_Present</t>
+  </si>
+  <si>
+    <t>Attendance_%</t>
+  </si>
+  <si>
+    <t>46083A8C</t>
+  </si>
+  <si>
+    <t>Rayan Martin Turay</t>
+  </si>
+  <si>
+    <t>FA50CA35</t>
+  </si>
+  <si>
+    <t>Abdul Karim Koroma</t>
+  </si>
+  <si>
+    <t>35E98EE0</t>
+  </si>
+  <si>
+    <t>Foday Kamara</t>
+  </si>
+  <si>
+    <t>Moses Sutton</t>
+  </si>
+  <si>
+    <t>Osman Abdul Salam Sesay</t>
+  </si>
+  <si>
+    <t>Saffa Wuya Jimmy</t>
+  </si>
+  <si>
+    <t>Lisa Kadija Abass Wurie</t>
+  </si>
+  <si>
+    <t>Amadu Jalloh</t>
+  </si>
+  <si>
+    <t>Mariama Hawanatu Conteh</t>
+  </si>
+  <si>
+    <t>Gibril Bangura</t>
+  </si>
+  <si>
+    <t>Abubakarr Bah</t>
+  </si>
+  <si>
+    <t>Franklin Danner</t>
+  </si>
+  <si>
+    <t>Sabrina Kandeh</t>
+  </si>
+  <si>
+    <t>Donald Sheku</t>
+  </si>
+  <si>
+    <t>Alpha Abubakarr Leigh</t>
+  </si>
+  <si>
+    <t>Alhaji Mawiya Sow</t>
+  </si>
+  <si>
+    <t>Charles Nyakeh Ensah</t>
+  </si>
+  <si>
+    <t>Abdul Aziz Sesay</t>
+  </si>
+  <si>
+    <t>Alfreda Victoria Dumbuya</t>
+  </si>
+  <si>
+    <t>Oluwayemisi Zipporah Delanjo-Obiwole</t>
+  </si>
+  <si>
+    <t>Eric Sahr Fabu</t>
+  </si>
+  <si>
+    <t>John Adel Sesay</t>
+  </si>
+  <si>
+    <t>Sharon Ramatha Koroma</t>
+  </si>
+  <si>
+    <t>Hawanatu Kamara</t>
+  </si>
+  <si>
+    <t>Ibrahim Sorie</t>
+  </si>
+  <si>
     <t>Ibrahim Kai-Samba</t>
-  </si>
-  <si>
-    <t>Ibrahim Sorie</t>
-  </si>
-  <si>
-    <t>Hawanatu Kamara</t>
-  </si>
-  <si>
-    <t>Sharon Ramatha Koroma</t>
-  </si>
-  <si>
-    <t>John Adel Sesay</t>
-  </si>
-  <si>
-    <t>Eric Sahr Fabu</t>
-  </si>
-  <si>
-    <t>Oluwayemisi Zipporah Delanjo-Obiwole</t>
-  </si>
-  <si>
-    <t>Alfreda Victoria Dumbuya</t>
-  </si>
-  <si>
-    <t>Abdul Aziz Sesay</t>
-  </si>
-  <si>
-    <t>Charles Nyakeh Ensah</t>
-  </si>
-  <si>
-    <t>Alhaji Mawiya Sow</t>
-  </si>
-  <si>
-    <t>Alpha Abubakarr Leigh</t>
-  </si>
-  <si>
-    <t>Donald Sheku</t>
-  </si>
-  <si>
-    <t>Sabrina Kandeh</t>
-  </si>
-  <si>
-    <t>Franklin Danner</t>
-  </si>
-  <si>
-    <t>Abubakarr Bah</t>
-  </si>
-  <si>
-    <t>Gibril Bangura</t>
-  </si>
-  <si>
-    <t>Mariama Hawanatu Conteh</t>
-  </si>
-  <si>
-    <t>Amadu Jalloh</t>
-  </si>
-  <si>
-    <t>Lisa Kadija Abass Wurie</t>
-  </si>
-  <si>
-    <t>Saffa Wuya Jimmy</t>
-  </si>
-  <si>
-    <t>Osman Abdul Salam Sesay</t>
-  </si>
-  <si>
-    <t>Moses Sutton</t>
-  </si>
-  <si>
-    <t>Foday Kamara</t>
-  </si>
-  <si>
-    <t>35E98EE0</t>
-  </si>
-  <si>
-    <t>Abdul Karim Koroma</t>
-  </si>
-  <si>
-    <t>FA50CA35</t>
-  </si>
-  <si>
-    <t>Rayan Martin Turay</t>
-  </si>
-  <si>
-    <t>46083A8C</t>
-  </si>
-  <si>
-    <t>Attendance_%</t>
-  </si>
-  <si>
-    <t>Total_Present</t>
-  </si>
-  <si>
-    <t>Week12_Status</t>
-  </si>
-  <si>
-    <t>Week12_Departure</t>
-  </si>
-  <si>
-    <t>Week12_Arrival</t>
-  </si>
-  <si>
-    <t>Week11_Status</t>
-  </si>
-  <si>
-    <t>Week11_Departure</t>
-  </si>
-  <si>
-    <t>Week11_Arrival</t>
-  </si>
-  <si>
-    <t>Week10_Status</t>
-  </si>
-  <si>
-    <t>Week10_Departure</t>
-  </si>
-  <si>
-    <t>Week10_Arrival</t>
-  </si>
-  <si>
-    <t>Week9_Status</t>
-  </si>
-  <si>
-    <t>Week9_Departure</t>
-  </si>
-  <si>
-    <t>Week9_Arrival</t>
-  </si>
-  <si>
-    <t>Week8_Status</t>
-  </si>
-  <si>
-    <t>Week8_Departure</t>
-  </si>
-  <si>
-    <t>Week8_Arrival</t>
-  </si>
-  <si>
-    <t>Week7_Status</t>
-  </si>
-  <si>
-    <t>Week7_Departure</t>
-  </si>
-  <si>
-    <t>Week7_Arrival</t>
-  </si>
-  <si>
-    <t>Week6_Status</t>
-  </si>
-  <si>
-    <t>Week6_Departure</t>
-  </si>
-  <si>
-    <t>Week6_Arrival</t>
-  </si>
-  <si>
-    <t>Week5_Status</t>
-  </si>
-  <si>
-    <t>Week5_Departure</t>
-  </si>
-  <si>
-    <t>Week5_Arrival</t>
-  </si>
-  <si>
-    <t>Week4_Status</t>
-  </si>
-  <si>
-    <t>Week4_Departure</t>
-  </si>
-  <si>
-    <t>Week4_Arrival</t>
-  </si>
-  <si>
-    <t>Week3_Status</t>
-  </si>
-  <si>
-    <t>Week3_Departure</t>
-  </si>
-  <si>
-    <t>Week3_Arrival</t>
-  </si>
-  <si>
-    <t>Week2_Status</t>
-  </si>
-  <si>
-    <t>Week2_Departure</t>
-  </si>
-  <si>
-    <t>Week2_Arrival</t>
-  </si>
-  <si>
-    <t>Week1_Status</t>
-  </si>
-  <si>
-    <t>Week1_Departure</t>
-  </si>
-  <si>
-    <t>Week1_Arrival</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Student_ID</t>
-  </si>
-  <si>
-    <t>RFID_UID</t>
   </si>
 </sst>
 </file>
@@ -277,7 +272,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -300,44 +295,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -364,15 +359,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -399,7 +393,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -411,142 +404,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -557,138 +574,138 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
         <v>40</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>905005656</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -735,13 +752,13 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>905005267</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -788,13 +805,13 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>905005334</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -833,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.3">
@@ -844,7 +861,7 @@
         <v>905005996</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -894,7 +911,7 @@
         <v>905005700</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -944,7 +961,7 @@
         <v>905006059</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -994,7 +1011,7 @@
         <v>905005935</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1044,7 +1061,7 @@
         <v>905005971</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1094,7 +1111,7 @@
         <v>905005966</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1144,7 +1161,7 @@
         <v>905005708</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1194,7 +1211,7 @@
         <v>905005724</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1244,7 +1261,7 @@
         <v>905005268</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1294,7 +1311,7 @@
         <v>905005613</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1344,7 +1361,7 @@
         <v>905005922</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1394,7 +1411,7 @@
         <v>905006066</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1444,7 +1461,7 @@
         <v>905005175</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1494,7 +1511,7 @@
         <v>905006142</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1544,7 +1561,7 @@
         <v>905005987</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1594,7 +1611,7 @@
         <v>905005462</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1644,7 +1661,7 @@
         <v>905005970</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1694,7 +1711,7 @@
         <v>905005965</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1744,7 +1761,7 @@
         <v>905005252</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1794,7 +1811,7 @@
         <v>905006201</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1844,7 +1861,7 @@
         <v>905005166</v>
       </c>
       <c r="C25" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1894,7 +1911,7 @@
         <v>905006001</v>
       </c>
       <c r="C26" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1944,7 +1961,7 @@
         <v>905005408</v>
       </c>
       <c r="C27" t="s">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1990,6 +2007,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>